--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_3_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_3_IN_Piura.xlsx
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>32.85</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C11" s="29">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>38.09</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>27.84</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>1.22</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1914,11 +1914,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>459.2947</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>325.8134</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>70.94</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1964,11 +1964,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>133.4813</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>29.06</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2162,11 +2162,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>459.5323</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2285,6 +2285,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2462,6 +2463,7 @@
       <c r="F14" s="17" t="inlineStr"/>
       <c r="G14" s="17" t="inlineStr"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
@@ -2508,6 +2510,7 @@
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19" ht="108" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
@@ -2727,11 +2730,11 @@
       </c>
       <c r="B12" s="32">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>814.65</v>
       </c>
       <c r="C12" s="23">
         <f>SUM(C10:C11)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -2741,19 +2744,19 @@
       <c r="E12" s="17" t="inlineStr"/>
       <c r="F12" s="17">
         <f>ROUND(AVERAGE(F10:F11),2)</f>
-        <v/>
+        <v>19.84</v>
       </c>
       <c r="G12" s="22">
         <f>ROUND(AVERAGE(G10:G11),4)</f>
-        <v/>
+        <v>0.441</v>
       </c>
       <c r="H12" s="23">
         <f>ROUND(AVERAGE(H10:H11),2)</f>
-        <v/>
+        <v>28.68</v>
       </c>
       <c r="I12" s="23">
         <f>ROUND(AVERAGE(I10:I11),2)</f>
-        <v/>
+        <v>64.19</v>
       </c>
     </row>
     <row r="13"/>
